--- a/data/performance/daily/signal_list_2026-07-22.xlsx
+++ b/data/performance/daily/signal_list_2026-07-22.xlsx
@@ -2055,7 +2055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J164"/>
+  <dimension ref="A1:J165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2080,7 +2080,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Win Rate: 35.6%  (57W / 103L of 160 evaluated)</t>
+          <t>Win Rate: 36.0%  (58W / 103L of 161 evaluated)</t>
         </is>
       </c>
     </row>
@@ -8851,6 +8851,48 @@
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>evaluated</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>LUCK.JK</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SCALPING_HIGH</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>103</v>
+      </c>
+      <c r="D165" t="n">
+        <v>119</v>
+      </c>
+      <c r="E165" t="n">
+        <v>132</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>28.16</v>
+      </c>
+      <c r="G165" s="4" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="H165" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-22.xlsx
+++ b/data/performance/daily/signal_list_2026-07-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/data/performance/daily/signal_list_2026-07-22.xlsx
+++ b/data/performance/daily/signal_list_2026-07-22.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Swing" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swing" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scalping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -461,9 +461,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,7 +494,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -518,15 +519,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -563,12 +569,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -600,17 +611,22 @@
       <c r="G6" s="4" t="n">
         <v>-3.62</v>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -642,17 +658,22 @@
       <c r="G7" s="4" t="n">
         <v>-1.91</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -684,17 +705,22 @@
       <c r="G8" s="4" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -726,17 +752,22 @@
       <c r="G9" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -773,12 +804,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -815,12 +851,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -852,17 +893,22 @@
       <c r="G12" s="4" t="n">
         <v>-3.72</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -899,12 +945,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -941,12 +992,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -978,17 +1034,22 @@
       <c r="G15" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1025,12 +1086,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1062,17 +1128,22 @@
       <c r="G17" s="4" t="n">
         <v>-1.81</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1109,12 +1180,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1151,12 +1227,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1193,12 +1274,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1235,12 +1321,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1277,12 +1368,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1319,12 +1415,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1356,17 +1457,22 @@
       <c r="G24" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1398,17 +1504,22 @@
       <c r="G25" s="4" t="n">
         <v>-2.38</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1440,17 +1551,22 @@
       <c r="G26" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1487,12 +1603,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1524,17 +1645,22 @@
       <c r="G28" s="4" t="n">
         <v>-0.68</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1566,17 +1692,22 @@
       <c r="G29" s="4" t="n">
         <v>-0.62</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1608,17 +1739,22 @@
       <c r="G30" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1655,12 +1791,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1697,12 +1838,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1739,12 +1885,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1781,12 +1932,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1818,17 +1974,22 @@
       <c r="G35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1860,17 +2021,22 @@
       <c r="G36" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1902,17 +2068,22 @@
       <c r="G37" s="4" t="n">
         <v>-14.29</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1949,12 +2120,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -1991,12 +2167,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2033,12 +2214,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2055,7 +2241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J165"/>
+  <dimension ref="A1:K165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2065,9 +2251,10 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="6" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2097,7 +2284,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Prev</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2122,15 +2309,20 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>W/L</t>
+          <t>W/L High</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
+          <t>W/L Close</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Eval Date</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2167,12 +2359,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2209,12 +2406,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2246,17 +2448,22 @@
       <c r="G7" s="4" t="n">
         <v>-4.29</v>
       </c>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2288,17 +2495,22 @@
       <c r="G8" s="4" t="n">
         <v>-3.62</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2335,12 +2547,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2377,12 +2594,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2414,17 +2636,22 @@
       <c r="G11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2456,17 +2683,22 @@
       <c r="G12" s="4" t="n">
         <v>-2.33</v>
       </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2498,17 +2730,22 @@
       <c r="G13" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2540,17 +2777,22 @@
       <c r="G14" s="4" t="n">
         <v>-0.4</v>
       </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2582,17 +2824,22 @@
       <c r="G15" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2629,12 +2876,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2666,17 +2918,22 @@
       <c r="G17" s="4" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2713,12 +2970,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2750,17 +3012,22 @@
       <c r="G19" s="4" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2792,17 +3059,22 @@
       <c r="G20" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2839,12 +3111,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2876,17 +3153,22 @@
       <c r="G22" s="4" t="n">
         <v>-1.39</v>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2918,17 +3200,22 @@
       <c r="G23" s="4" t="n">
         <v>-1.63</v>
       </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -2965,12 +3252,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3002,17 +3294,22 @@
       <c r="G25" s="4" t="n">
         <v>-2.42</v>
       </c>
-      <c r="H25" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3044,17 +3341,22 @@
       <c r="G26" s="4" t="n">
         <v>-1.61</v>
       </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3086,17 +3388,22 @@
       <c r="G27" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H27" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3133,12 +3440,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3170,17 +3482,22 @@
       <c r="G29" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3212,17 +3529,22 @@
       <c r="G30" s="4" t="n">
         <v>-2.44</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3254,17 +3576,22 @@
       <c r="G31" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3296,17 +3623,22 @@
       <c r="G32" s="4" t="n">
         <v>-1.92</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3338,17 +3670,22 @@
       <c r="G33" s="4" t="n">
         <v>-0.73</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3380,17 +3717,22 @@
       <c r="G34" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3427,12 +3769,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3469,12 +3816,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3506,17 +3858,22 @@
       <c r="G37" s="4" t="n">
         <v>-3.72</v>
       </c>
-      <c r="H37" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3548,17 +3905,22 @@
       <c r="G38" s="4" t="n">
         <v>-6.37</v>
       </c>
-      <c r="H38" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3595,12 +3957,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3637,12 +4004,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3679,12 +4051,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3716,17 +4093,22 @@
       <c r="G42" s="4" t="n">
         <v>-0.86</v>
       </c>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3763,12 +4145,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3800,17 +4187,22 @@
       <c r="G44" s="4" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H44" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3842,17 +4234,22 @@
       <c r="G45" s="4" t="n">
         <v>-1.52</v>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3884,17 +4281,22 @@
       <c r="G46" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3926,17 +4328,22 @@
       <c r="G47" s="4" t="n">
         <v>-1.78</v>
       </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -3968,17 +4375,22 @@
       <c r="G48" s="4" t="n">
         <v>-0.95</v>
       </c>
-      <c r="H48" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4010,17 +4422,22 @@
       <c r="G49" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H49" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4057,12 +4474,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4099,12 +4521,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4136,17 +4563,22 @@
       <c r="G52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4178,17 +4610,22 @@
       <c r="G53" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4220,17 +4657,22 @@
       <c r="G54" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4262,17 +4704,22 @@
       <c r="G55" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4304,17 +4751,22 @@
       <c r="G56" s="4" t="n">
         <v>-4.49</v>
       </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4346,17 +4798,22 @@
       <c r="G57" s="4" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H57" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4393,12 +4850,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4430,17 +4892,22 @@
       <c r="G59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4477,12 +4944,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4514,17 +4986,22 @@
       <c r="G61" s="4" t="n">
         <v>-1.19</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4556,17 +5033,22 @@
       <c r="G62" s="4" t="n">
         <v>-1.81</v>
       </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4603,12 +5085,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4645,12 +5132,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4687,12 +5179,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4729,12 +5226,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4771,12 +5273,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4813,12 +5320,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4855,12 +5367,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4892,17 +5409,22 @@
       <c r="G70" s="4" t="n">
         <v>-6.47</v>
       </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4934,17 +5456,22 @@
       <c r="G71" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -4981,12 +5508,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5018,17 +5550,22 @@
       <c r="G73" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5065,12 +5602,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5107,12 +5649,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I75" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5144,17 +5691,22 @@
       <c r="G76" s="4" t="n">
         <v>-1.09</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5186,17 +5738,22 @@
       <c r="G77" s="4" t="n">
         <v>-1.56</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5233,12 +5790,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5275,12 +5837,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5317,12 +5884,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5354,17 +5926,22 @@
       <c r="G81" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H81" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5401,12 +5978,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5438,17 +6020,22 @@
       <c r="G83" s="4" t="n">
         <v>-3.84</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5480,17 +6067,22 @@
       <c r="G84" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H84" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5527,12 +6119,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5564,17 +6161,22 @@
       <c r="G86" s="4" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5611,12 +6213,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5648,17 +6255,22 @@
       <c r="G88" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5695,12 +6307,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I89" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5737,12 +6354,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5779,12 +6401,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5821,12 +6448,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5863,12 +6495,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5905,12 +6542,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5942,17 +6584,22 @@
       <c r="G95" s="4" t="n">
         <v>-2.65</v>
       </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H95" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -5984,17 +6631,22 @@
       <c r="G96" s="4" t="n">
         <v>-0.88</v>
       </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H96" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6026,17 +6678,22 @@
       <c r="G97" s="4" t="n">
         <v>-3.42</v>
       </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H97" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6073,12 +6730,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6115,12 +6777,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I99" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6152,17 +6819,22 @@
       <c r="G100" s="4" t="n">
         <v>-2.36</v>
       </c>
-      <c r="H100" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H100" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6194,17 +6866,22 @@
       <c r="G101" s="4" t="n">
         <v>-1.4</v>
       </c>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6241,12 +6918,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I102" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6278,17 +6960,22 @@
       <c r="G103" s="4" t="n">
         <v>-1.15</v>
       </c>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6325,12 +7012,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6367,12 +7059,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6409,12 +7106,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6451,12 +7153,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I107" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6493,12 +7200,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6530,17 +7242,22 @@
       <c r="G109" s="4" t="n">
         <v>-2.29</v>
       </c>
-      <c r="H109" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H109" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6572,17 +7289,22 @@
       <c r="G110" s="4" t="n">
         <v>-2.78</v>
       </c>
-      <c r="H110" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H110" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6619,12 +7341,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I111" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6661,12 +7388,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6703,12 +7435,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I113" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6740,17 +7477,22 @@
       <c r="G114" s="4" t="n">
         <v>-6.09</v>
       </c>
-      <c r="H114" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H114" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6787,12 +7529,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6824,17 +7571,22 @@
       <c r="G116" s="4" t="n">
         <v>-2.1</v>
       </c>
-      <c r="H116" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H116" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6871,12 +7623,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I117" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6913,12 +7670,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I118" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6955,12 +7717,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I119" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -6997,12 +7764,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7034,17 +7806,22 @@
       <c r="G121" s="4" t="n">
         <v>-3.85</v>
       </c>
-      <c r="H121" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H121" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7081,12 +7858,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I122" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7118,17 +7900,22 @@
       <c r="G123" s="4" t="n">
         <v>-6.59</v>
       </c>
-      <c r="H123" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H123" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7165,12 +7952,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I124" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7207,12 +7999,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7244,17 +8041,22 @@
       <c r="G126" s="4" t="n">
         <v>-0.58</v>
       </c>
-      <c r="H126" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H126" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7286,17 +8088,22 @@
       <c r="G127" s="4" t="n">
         <v>-1.54</v>
       </c>
-      <c r="H127" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H127" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7328,17 +8135,22 @@
       <c r="G128" s="4" t="n">
         <v>-1.69</v>
       </c>
-      <c r="H128" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H128" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7370,17 +8182,22 @@
       <c r="G129" s="4" t="n">
         <v>-4.11</v>
       </c>
-      <c r="H129" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H129" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7412,17 +8229,22 @@
       <c r="G130" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H130" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H130" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7459,12 +8281,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I131" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7501,12 +8328,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I132" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7538,17 +8370,22 @@
       <c r="G133" s="4" t="n">
         <v>-7.25</v>
       </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H133" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7580,17 +8417,22 @@
       <c r="G134" s="4" t="n">
         <v>-6.25</v>
       </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H134" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7627,12 +8469,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7664,17 +8511,22 @@
       <c r="G136" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H136" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H136" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7711,12 +8563,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I137" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7748,17 +8605,22 @@
       <c r="G138" s="4" t="n">
         <v>-14.29</v>
       </c>
-      <c r="H138" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H138" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7790,17 +8652,22 @@
       <c r="G139" s="4" t="n">
         <v>-2.04</v>
       </c>
-      <c r="H139" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H139" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7832,17 +8699,22 @@
       <c r="G140" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H140" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H140" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7879,12 +8751,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I141" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7916,17 +8793,22 @@
       <c r="G142" s="4" t="n">
         <v>-3.26</v>
       </c>
-      <c r="H142" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H142" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -7958,17 +8840,22 @@
       <c r="G143" s="4" t="n">
         <v>-1.68</v>
       </c>
-      <c r="H143" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H143" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8000,17 +8887,22 @@
       <c r="G144" s="4" t="n">
         <v>-0.7</v>
       </c>
-      <c r="H144" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H144" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8042,17 +8934,22 @@
       <c r="G145" s="4" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="H145" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H145" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8089,12 +8986,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I146" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8131,12 +9033,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8168,17 +9075,22 @@
       <c r="G148" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H148" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H148" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8215,12 +9127,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8257,12 +9174,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I150" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8299,12 +9221,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I151" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8341,12 +9268,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I152" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8383,12 +9315,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I153" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8420,17 +9357,22 @@
       <c r="G154" s="4" t="n">
         <v>-1.55</v>
       </c>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8462,17 +9404,22 @@
       <c r="G155" s="4" t="n">
         <v>-1.27</v>
       </c>
-      <c r="H155" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H155" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8504,17 +9451,22 @@
       <c r="G156" s="4" t="n">
         <v>-2.26</v>
       </c>
-      <c r="H156" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H156" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8551,12 +9503,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I157" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8588,17 +9545,22 @@
       <c r="G158" s="4" t="n">
         <v>-0.93</v>
       </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H158" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8635,12 +9597,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I159" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8672,17 +9639,22 @@
       <c r="G160" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H160" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H160" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8714,17 +9686,22 @@
       <c r="G161" s="4" t="n">
         <v>-0.49</v>
       </c>
-      <c r="H161" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H161" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8756,17 +9733,22 @@
       <c r="G162" s="4" t="n">
         <v>-1.72</v>
       </c>
-      <c r="H162" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H162" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8803,12 +9785,17 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8840,17 +9827,22 @@
       <c r="G164" s="4" t="n">
         <v>-0.65</v>
       </c>
-      <c r="H164" s="6" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="H164" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>L</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>
@@ -8887,12 +9879,17 @@
           <t>W</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+      <c r="I165" s="5" t="inlineStr">
+        <is>
+          <t>W</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
         <is>
           <t>evaluated</t>
         </is>

--- a/data/performance/daily/signal_list_2026-07-22.xlsx
+++ b/data/performance/daily/signal_list_2026-07-22.xlsx
@@ -559,7 +559,7 @@
         <v>865</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>875</v>
       </c>
       <c r="E5" t="n">
         <v>960</v>
@@ -609,7 +609,7 @@
         <v>1380</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>1380</v>
       </c>
       <c r="E6" t="n">
         <v>1330</v>
@@ -659,7 +659,7 @@
         <v>785</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>775</v>
       </c>
       <c r="E7" t="n">
         <v>770</v>
@@ -709,7 +709,7 @@
         <v>4260</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>4260</v>
       </c>
       <c r="E8" t="n">
         <v>4200</v>
@@ -759,7 +759,7 @@
         <v>790</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>790</v>
       </c>
       <c r="E9" t="n">
         <v>790</v>
@@ -809,7 +809,7 @@
         <v>1010</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>1010</v>
       </c>
       <c r="E10" t="n">
         <v>950</v>
@@ -859,7 +859,7 @@
         <v>224</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>226</v>
       </c>
       <c r="E11" t="n">
         <v>226</v>
@@ -909,7 +909,7 @@
         <v>940</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E12" t="n">
         <v>905</v>
@@ -959,7 +959,7 @@
         <v>284</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>296</v>
       </c>
       <c r="E13" t="n">
         <v>294</v>
@@ -1009,7 +1009,7 @@
         <v>3150</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>3240</v>
       </c>
       <c r="E14" t="n">
         <v>3340</v>
@@ -1059,7 +1059,7 @@
         <v>17450</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>17550</v>
       </c>
       <c r="E15" t="n">
         <v>17300</v>
@@ -1109,7 +1109,7 @@
         <v>1140</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>1140</v>
       </c>
       <c r="E16" t="n">
         <v>1145</v>
@@ -1159,7 +1159,7 @@
         <v>2770</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>2770</v>
       </c>
       <c r="E17" t="n">
         <v>2720</v>
@@ -1209,7 +1209,7 @@
         <v>21475</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="E18" t="n">
         <v>21650</v>
@@ -1259,7 +1259,7 @@
         <v>1300</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>1425</v>
       </c>
       <c r="E19" t="n">
         <v>1625</v>
@@ -1309,7 +1309,7 @@
         <v>990</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>995</v>
       </c>
       <c r="E20" t="n">
         <v>995</v>
@@ -1359,7 +1359,7 @@
         <v>535</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E21" t="n">
         <v>515</v>
@@ -1409,7 +1409,7 @@
         <v>1580</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>1580</v>
       </c>
       <c r="E22" t="n">
         <v>1570</v>
@@ -1459,7 +1459,7 @@
         <v>3800</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>3800</v>
       </c>
       <c r="E23" t="n">
         <v>3910</v>
@@ -1509,7 +1509,7 @@
         <v>960</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>970</v>
       </c>
       <c r="E24" t="n">
         <v>945</v>
@@ -1559,7 +1559,7 @@
         <v>84</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E25" t="n">
         <v>82</v>
@@ -1609,7 +1609,7 @@
         <v>71</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
         <v>71</v>
@@ -1659,7 +1659,7 @@
         <v>1760</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>1760</v>
       </c>
       <c r="E27" t="n">
         <v>1750</v>
@@ -1709,7 +1709,7 @@
         <v>730</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>730</v>
       </c>
       <c r="E28" t="n">
         <v>725</v>
@@ -1759,7 +1759,7 @@
         <v>320</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>320</v>
       </c>
       <c r="E29" t="n">
         <v>318</v>
@@ -1809,7 +1809,7 @@
         <v>1235</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>1235</v>
       </c>
       <c r="E30" t="n">
         <v>1230</v>
@@ -1859,7 +1859,7 @@
         <v>1250</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1250</v>
       </c>
       <c r="E31" t="n">
         <v>1220</v>
@@ -1909,7 +1909,7 @@
         <v>191</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>191</v>
       </c>
       <c r="E32" t="n">
         <v>192</v>
@@ -1959,7 +1959,7 @@
         <v>8450</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>8450</v>
       </c>
       <c r="E33" t="n">
         <v>8525</v>
@@ -2009,7 +2009,7 @@
         <v>520</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>520</v>
       </c>
       <c r="E34" t="n">
         <v>515</v>
@@ -2059,7 +2059,7 @@
         <v>740</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>745</v>
       </c>
       <c r="E35" t="n">
         <v>740</v>
@@ -2109,7 +2109,7 @@
         <v>93</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>94</v>
       </c>
       <c r="E36" t="n">
         <v>93</v>
@@ -2159,7 +2159,7 @@
         <v>133</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E37" t="n">
         <v>114</v>
@@ -2209,7 +2209,7 @@
         <v>725</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>725</v>
       </c>
       <c r="E38" t="n">
         <v>715</v>
@@ -2259,7 +2259,7 @@
         <v>156</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>156</v>
       </c>
       <c r="E39" t="n">
         <v>157</v>
@@ -2309,7 +2309,7 @@
         <v>2540</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>2550</v>
       </c>
       <c r="E40" t="n">
         <v>2580</v>
@@ -2463,7 +2463,7 @@
         <v>172</v>
       </c>
       <c r="D5" t="n">
-        <v/>
+        <v>169</v>
       </c>
       <c r="E5" t="n">
         <v>165</v>
@@ -2513,7 +2513,7 @@
         <v>865</v>
       </c>
       <c r="D6" t="n">
-        <v/>
+        <v>875</v>
       </c>
       <c r="E6" t="n">
         <v>960</v>
@@ -2563,7 +2563,7 @@
         <v>140</v>
       </c>
       <c r="D7" t="n">
-        <v/>
+        <v>140</v>
       </c>
       <c r="E7" t="n">
         <v>134</v>
@@ -2613,7 +2613,7 @@
         <v>1380</v>
       </c>
       <c r="D8" t="n">
-        <v/>
+        <v>1380</v>
       </c>
       <c r="E8" t="n">
         <v>1330</v>
@@ -2663,7 +2663,7 @@
         <v>125</v>
       </c>
       <c r="D9" t="n">
-        <v/>
+        <v>125</v>
       </c>
       <c r="E9" t="n">
         <v>124</v>
@@ -2713,7 +2713,7 @@
         <v>118</v>
       </c>
       <c r="D10" t="n">
-        <v/>
+        <v>120</v>
       </c>
       <c r="E10" t="n">
         <v>120</v>
@@ -2763,7 +2763,7 @@
         <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v/>
+        <v>55</v>
       </c>
       <c r="E11" t="n">
         <v>55</v>
@@ -2813,7 +2813,7 @@
         <v>645</v>
       </c>
       <c r="D12" t="n">
-        <v/>
+        <v>670</v>
       </c>
       <c r="E12" t="n">
         <v>630</v>
@@ -2863,7 +2863,7 @@
         <v>3070</v>
       </c>
       <c r="D13" t="n">
-        <v/>
+        <v>3080</v>
       </c>
       <c r="E13" t="n">
         <v>3020</v>
@@ -2913,7 +2913,7 @@
         <v>1265</v>
       </c>
       <c r="D14" t="n">
-        <v/>
+        <v>1265</v>
       </c>
       <c r="E14" t="n">
         <v>1260</v>
@@ -2963,7 +2963,7 @@
         <v>262</v>
       </c>
       <c r="D15" t="n">
-        <v/>
+        <v>264</v>
       </c>
       <c r="E15" t="n">
         <v>262</v>
@@ -3013,7 +3013,7 @@
         <v>116</v>
       </c>
       <c r="D16" t="n">
-        <v/>
+        <v>116</v>
       </c>
       <c r="E16" t="n">
         <v>114</v>
@@ -3063,7 +3063,7 @@
         <v>4260</v>
       </c>
       <c r="D17" t="n">
-        <v/>
+        <v>4260</v>
       </c>
       <c r="E17" t="n">
         <v>4200</v>
@@ -3113,7 +3113,7 @@
         <v>162</v>
       </c>
       <c r="D18" t="n">
-        <v/>
+        <v>163</v>
       </c>
       <c r="E18" t="n">
         <v>164</v>
@@ -3163,7 +3163,7 @@
         <v>670</v>
       </c>
       <c r="D19" t="n">
-        <v/>
+        <v>670</v>
       </c>
       <c r="E19" t="n">
         <v>660</v>
@@ -3213,7 +3213,7 @@
         <v>790</v>
       </c>
       <c r="D20" t="n">
-        <v/>
+        <v>790</v>
       </c>
       <c r="E20" t="n">
         <v>790</v>
@@ -3263,7 +3263,7 @@
         <v>155</v>
       </c>
       <c r="D21" t="n">
-        <v/>
+        <v>157</v>
       </c>
       <c r="E21" t="n">
         <v>158</v>
@@ -3313,7 +3313,7 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
         <v>71</v>
@@ -3363,7 +3363,7 @@
         <v>123</v>
       </c>
       <c r="D23" t="n">
-        <v/>
+        <v>124</v>
       </c>
       <c r="E23" t="n">
         <v>121</v>
@@ -3413,7 +3413,7 @@
         <v>107</v>
       </c>
       <c r="D24" t="n">
-        <v/>
+        <v>107</v>
       </c>
       <c r="E24" t="n">
         <v>115</v>
@@ -3463,7 +3463,7 @@
         <v>620</v>
       </c>
       <c r="D25" t="n">
-        <v/>
+        <v>625</v>
       </c>
       <c r="E25" t="n">
         <v>605</v>
@@ -3513,7 +3513,7 @@
         <v>1860</v>
       </c>
       <c r="D26" t="n">
-        <v/>
+        <v>1870</v>
       </c>
       <c r="E26" t="n">
         <v>1830</v>
@@ -3563,7 +3563,7 @@
         <v>168</v>
       </c>
       <c r="D27" t="n">
-        <v/>
+        <v>170</v>
       </c>
       <c r="E27" t="n">
         <v>168</v>
@@ -3613,7 +3613,7 @@
         <v>1010</v>
       </c>
       <c r="D28" t="n">
-        <v/>
+        <v>1010</v>
       </c>
       <c r="E28" t="n">
         <v>950</v>
@@ -3663,7 +3663,7 @@
         <v>94</v>
       </c>
       <c r="D29" t="n">
-        <v/>
+        <v>95</v>
       </c>
       <c r="E29" t="n">
         <v>94</v>
@@ -3713,7 +3713,7 @@
         <v>82</v>
       </c>
       <c r="D30" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E30" t="n">
         <v>80</v>
@@ -3763,7 +3763,7 @@
         <v>1560</v>
       </c>
       <c r="D31" t="n">
-        <v/>
+        <v>1560</v>
       </c>
       <c r="E31" t="n">
         <v>1560</v>
@@ -3813,7 +3813,7 @@
         <v>52</v>
       </c>
       <c r="D32" t="n">
-        <v/>
+        <v>52</v>
       </c>
       <c r="E32" t="n">
         <v>51</v>
@@ -3863,7 +3863,7 @@
         <v>137</v>
       </c>
       <c r="D33" t="n">
-        <v/>
+        <v>138</v>
       </c>
       <c r="E33" t="n">
         <v>136</v>
@@ -3913,7 +3913,7 @@
         <v>440</v>
       </c>
       <c r="D34" t="n">
-        <v/>
+        <v>442</v>
       </c>
       <c r="E34" t="n">
         <v>440</v>
@@ -3963,7 +3963,7 @@
         <v>224</v>
       </c>
       <c r="D35" t="n">
-        <v/>
+        <v>226</v>
       </c>
       <c r="E35" t="n">
         <v>226</v>
@@ -4013,7 +4013,7 @@
         <v>80</v>
       </c>
       <c r="D36" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E36" t="n">
         <v>83</v>
@@ -4063,7 +4063,7 @@
         <v>940</v>
       </c>
       <c r="D37" t="n">
-        <v/>
+        <v>950</v>
       </c>
       <c r="E37" t="n">
         <v>905</v>
@@ -4113,7 +4113,7 @@
         <v>157</v>
       </c>
       <c r="D38" t="n">
-        <v/>
+        <v>157</v>
       </c>
       <c r="E38" t="n">
         <v>147</v>
@@ -4163,7 +4163,7 @@
         <v>284</v>
       </c>
       <c r="D39" t="n">
-        <v/>
+        <v>296</v>
       </c>
       <c r="E39" t="n">
         <v>294</v>
@@ -4213,7 +4213,7 @@
         <v>3150</v>
       </c>
       <c r="D40" t="n">
-        <v/>
+        <v>3240</v>
       </c>
       <c r="E40" t="n">
         <v>3340</v>
@@ -4263,7 +4263,7 @@
         <v>91</v>
       </c>
       <c r="D41" t="n">
-        <v/>
+        <v>92</v>
       </c>
       <c r="E41" t="n">
         <v>93</v>
@@ -4313,7 +4313,7 @@
         <v>17450</v>
       </c>
       <c r="D42" t="n">
-        <v/>
+        <v>17550</v>
       </c>
       <c r="E42" t="n">
         <v>17300</v>
@@ -4363,7 +4363,7 @@
         <v>1140</v>
       </c>
       <c r="D43" t="n">
-        <v/>
+        <v>1140</v>
       </c>
       <c r="E43" t="n">
         <v>1145</v>
@@ -4413,7 +4413,7 @@
         <v>91</v>
       </c>
       <c r="D44" t="n">
-        <v/>
+        <v>91</v>
       </c>
       <c r="E44" t="n">
         <v>90</v>
@@ -4463,7 +4463,7 @@
         <v>132</v>
       </c>
       <c r="D45" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E45" t="n">
         <v>130</v>
@@ -4513,7 +4513,7 @@
         <v>157</v>
       </c>
       <c r="D46" t="n">
-        <v/>
+        <v>158</v>
       </c>
       <c r="E46" t="n">
         <v>155</v>
@@ -4563,7 +4563,7 @@
         <v>845</v>
       </c>
       <c r="D47" t="n">
-        <v/>
+        <v>845</v>
       </c>
       <c r="E47" t="n">
         <v>830</v>
@@ -4613,7 +4613,7 @@
         <v>1575</v>
       </c>
       <c r="D48" t="n">
-        <v/>
+        <v>1580</v>
       </c>
       <c r="E48" t="n">
         <v>1560</v>
@@ -4663,7 +4663,7 @@
         <v>164</v>
       </c>
       <c r="D49" t="n">
-        <v/>
+        <v>164</v>
       </c>
       <c r="E49" t="n">
         <v>164</v>
@@ -4713,7 +4713,7 @@
         <v>280</v>
       </c>
       <c r="D50" t="n">
-        <v/>
+        <v>284</v>
       </c>
       <c r="E50" t="n">
         <v>284</v>
@@ -4763,7 +4763,7 @@
         <v>2530</v>
       </c>
       <c r="D51" t="n">
-        <v/>
+        <v>2570</v>
       </c>
       <c r="E51" t="n">
         <v>2550</v>
@@ -4813,7 +4813,7 @@
         <v>7875</v>
       </c>
       <c r="D52" t="n">
-        <v/>
+        <v>7875</v>
       </c>
       <c r="E52" t="n">
         <v>7875</v>
@@ -4863,7 +4863,7 @@
         <v>142</v>
       </c>
       <c r="D53" t="n">
-        <v/>
+        <v>142</v>
       </c>
       <c r="E53" t="n">
         <v>142</v>
@@ -4913,7 +4913,7 @@
         <v>442</v>
       </c>
       <c r="D54" t="n">
-        <v/>
+        <v>434</v>
       </c>
       <c r="E54" t="n">
         <v>442</v>
@@ -4963,7 +4963,7 @@
         <v>136</v>
       </c>
       <c r="D55" t="n">
-        <v/>
+        <v>137</v>
       </c>
       <c r="E55" t="n">
         <v>136</v>
@@ -5013,7 +5013,7 @@
         <v>89</v>
       </c>
       <c r="D56" t="n">
-        <v/>
+        <v>89</v>
       </c>
       <c r="E56" t="n">
         <v>85</v>
@@ -5063,7 +5063,7 @@
         <v>71</v>
       </c>
       <c r="D57" t="n">
-        <v/>
+        <v>71</v>
       </c>
       <c r="E57" t="n">
         <v>70</v>
@@ -5113,7 +5113,7 @@
         <v>364</v>
       </c>
       <c r="D58" t="n">
-        <v/>
+        <v>364</v>
       </c>
       <c r="E58" t="n">
         <v>354</v>
@@ -5163,7 +5163,7 @@
         <v>63</v>
       </c>
       <c r="D59" t="n">
-        <v/>
+        <v>64</v>
       </c>
       <c r="E59" t="n">
         <v>63</v>
@@ -5213,7 +5213,7 @@
         <v>256</v>
       </c>
       <c r="D60" t="n">
-        <v/>
+        <v>260</v>
       </c>
       <c r="E60" t="n">
         <v>266</v>
@@ -5263,7 +5263,7 @@
         <v>84</v>
       </c>
       <c r="D61" t="n">
-        <v/>
+        <v>83</v>
       </c>
       <c r="E61" t="n">
         <v>83</v>
@@ -5313,7 +5313,7 @@
         <v>2770</v>
       </c>
       <c r="D62" t="n">
-        <v/>
+        <v>2770</v>
       </c>
       <c r="E62" t="n">
         <v>2720</v>
@@ -5363,7 +5363,7 @@
         <v>82</v>
       </c>
       <c r="D63" t="n">
-        <v/>
+        <v>81</v>
       </c>
       <c r="E63" t="n">
         <v>104</v>
@@ -5413,7 +5413,7 @@
         <v>21475</v>
       </c>
       <c r="D64" t="n">
-        <v/>
+        <v>21500</v>
       </c>
       <c r="E64" t="n">
         <v>21650</v>
@@ -5463,7 +5463,7 @@
         <v>94</v>
       </c>
       <c r="D65" t="n">
-        <v/>
+        <v>96</v>
       </c>
       <c r="E65" t="n">
         <v>98</v>
@@ -5513,7 +5513,7 @@
         <v>1300</v>
       </c>
       <c r="D66" t="n">
-        <v/>
+        <v>1425</v>
       </c>
       <c r="E66" t="n">
         <v>1625</v>
@@ -5563,7 +5563,7 @@
         <v>222</v>
       </c>
       <c r="D67" t="n">
-        <v/>
+        <v>222</v>
       </c>
       <c r="E67" t="n">
         <v>214</v>
@@ -5613,7 +5613,7 @@
         <v>152</v>
       </c>
       <c r="D68" t="n">
-        <v/>
+        <v>155</v>
       </c>
       <c r="E68" t="n">
         <v>155</v>
@@ -5663,7 +5663,7 @@
         <v>535</v>
       </c>
       <c r="D69" t="n">
-        <v/>
+        <v>535</v>
       </c>
       <c r="E69" t="n">
         <v>515</v>
@@ -5713,7 +5713,7 @@
         <v>1160</v>
       </c>
       <c r="D70" t="n">
-        <v/>
+        <v>1205</v>
       </c>
       <c r="E70" t="n">
         <v>1085</v>
@@ -5763,7 +5763,7 @@
         <v>80</v>
       </c>
       <c r="D71" t="n">
-        <v/>
+        <v>80</v>
       </c>
       <c r="E71" t="n">
         <v>80</v>
@@ -5813,7 +5813,7 @@
         <v>3800</v>
       </c>
       <c r="D72" t="n">
-        <v/>
+        <v>3800</v>
       </c>
       <c r="E72" t="n">
         <v>3910</v>
@@ -5863,7 +5863,7 @@
         <v>216</v>
       </c>
       <c r="D73" t="n">
-        <v/>
+        <v>216</v>
       </c>
       <c r="E73" t="n">
         <v>216</v>
@@ -5913,7 +5913,7 @@
         <v>220</v>
       </c>
       <c r="D74" t="n">
-        <v/>
+        <v>218</v>
       </c>
       <c r="E74" t="n">
         <v>214</v>
@@ -5963,7 +5963,7 @@
         <v>4470</v>
       </c>
       <c r="D75" t="n">
-        <v/>
+        <v>4500</v>
       </c>
       <c r="E75" t="n">
         <v>4690</v>
@@ -6013,7 +6013,7 @@
         <v>920</v>
       </c>
       <c r="D76" t="n">
-        <v/>
+        <v>920</v>
       </c>
       <c r="E76" t="n">
         <v>910</v>
@@ -6063,7 +6063,7 @@
         <v>960</v>
       </c>
       <c r="D77" t="n">
-        <v/>
+        <v>970</v>
       </c>
       <c r="E77" t="n">
         <v>945</v>
@@ -6113,7 +6113,7 @@
         <v>500</v>
       </c>
       <c r="D78" t="n">
-        <v/>
+        <v>482</v>
       </c>
       <c r="E78" t="n">
         <v>486</v>
@@ -6163,7 +6163,7 @@
         <v>164</v>
       </c>
       <c r="D79" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="E79" t="n">
         <v>166</v>
@@ -6213,7 +6213,7 @@
         <v>322</v>
       </c>
       <c r="D80" t="n">
-        <v/>
+        <v>326</v>
       </c>
       <c r="E80" t="n">
         <v>332</v>
@@ -6263,7 +6263,7 @@
         <v>71</v>
       </c>
       <c r="D81" t="n">
-        <v/>
+        <v>72</v>
       </c>
       <c r="E81" t="n">
         <v>71</v>
@@ -6313,7 +6313,7 @@
         <v>1760</v>
       </c>
       <c r="D82" t="n">
-        <v/>
+        <v>1760</v>
       </c>
       <c r="E82" t="n">
         <v>1750</v>
@@ -6363,7 +6363,7 @@
         <v>1825</v>
       </c>
       <c r="D83" t="n">
-        <v/>
+        <v>1835</v>
       </c>
       <c r="E83" t="n">
         <v>1755</v>
@@ -6413,7 +6413,7 @@
         <v>930</v>
       </c>
       <c r="D84" t="n">
-        <v/>
+        <v>935</v>
       </c>
       <c r="E84" t="n">
         <v>930</v>
@@ -6463,7 +6463,7 @@
         <v>745</v>
       </c>
       <c r="D85" t="n">
-        <v/>
+        <v>745</v>
       </c>
       <c r="E85" t="n">
         <v>745</v>
@@ -6513,7 +6513,7 @@
         <v>6100</v>
       </c>
       <c r="D86" t="n">
-        <v/>
+        <v>6100</v>
       </c>
       <c r="E86" t="n">
         <v>6050</v>
@@ -6563,7 +6563,7 @@
         <v>478</v>
       </c>
       <c r="D87" t="n">
-        <v/>
+        <v>478</v>
       </c>
       <c r="E87" t="n">
         <v>488</v>
@@ -6613,7 +6613,7 @@
         <v>412</v>
       </c>
       <c r="D88" t="n">
-        <v/>
+        <v>412</v>
       </c>
       <c r="E88" t="n">
         <v>412</v>
@@ -6663,7 +6663,7 @@
         <v>2250</v>
       </c>
       <c r="D89" t="n">
-        <v/>
+        <v>2270</v>
       </c>
       <c r="E89" t="n">
         <v>2280</v>
@@ -6713,7 +6713,7 @@
         <v>106</v>
       </c>
       <c r="D90" t="n">
-        <v/>
+        <v>106</v>
       </c>
       <c r="E90" t="n">
         <v>107</v>
@@ -6763,7 +6763,7 @@
         <v>67</v>
       </c>
       <c r="D91" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E91" t="n">
         <v>72</v>
@@ -6813,7 +6813,7 @@
         <v>1190</v>
       </c>
       <c r="D92" t="n">
-        <v/>
+        <v>1190</v>
       </c>
       <c r="E92" t="n">
         <v>1200</v>
@@ -6863,7 +6863,7 @@
         <v>346</v>
       </c>
       <c r="D93" t="n">
-        <v/>
+        <v>346</v>
       </c>
       <c r="E93" t="n">
         <v>364</v>
@@ -6913,7 +6913,7 @@
         <v>89</v>
       </c>
       <c r="D94" t="n">
-        <v/>
+        <v>89</v>
       </c>
       <c r="E94" t="n">
         <v>90</v>
@@ -6963,7 +6963,7 @@
         <v>302</v>
       </c>
       <c r="D95" t="n">
-        <v/>
+        <v>302</v>
       </c>
       <c r="E95" t="n">
         <v>294</v>
@@ -7013,7 +7013,7 @@
         <v>114</v>
       </c>
       <c r="D96" t="n">
-        <v/>
+        <v>115</v>
       </c>
       <c r="E96" t="n">
         <v>113</v>
@@ -7063,7 +7063,7 @@
         <v>234</v>
       </c>
       <c r="D97" t="n">
-        <v/>
+        <v>240</v>
       </c>
       <c r="E97" t="n">
         <v>226</v>
@@ -7113,7 +7113,7 @@
         <v>665</v>
       </c>
       <c r="D98" t="n">
-        <v/>
+        <v>670</v>
       </c>
       <c r="E98" t="n">
         <v>705</v>
@@ -7163,7 +7163,7 @@
         <v>85</v>
       </c>
       <c r="D99" t="n">
-        <v/>
+        <v>86</v>
       </c>
       <c r="E99" t="n">
         <v>86</v>
@@ -7213,7 +7213,7 @@
         <v>635</v>
       </c>
       <c r="D100" t="n">
-        <v/>
+        <v>635</v>
       </c>
       <c r="E100" t="n">
         <v>620</v>
@@ -7263,7 +7263,7 @@
         <v>1070</v>
       </c>
       <c r="D101" t="n">
-        <v/>
+        <v>1075</v>
       </c>
       <c r="E101" t="n">
         <v>1055</v>
@@ -7313,7 +7313,7 @@
         <v>74</v>
       </c>
       <c r="D102" t="n">
-        <v/>
+        <v>75</v>
       </c>
       <c r="E102" t="n">
         <v>76</v>
@@ -7363,7 +7363,7 @@
         <v>6525</v>
       </c>
       <c r="D103" t="n">
-        <v/>
+        <v>6575</v>
       </c>
       <c r="E103" t="n">
         <v>6450</v>
@@ -7413,7 +7413,7 @@
         <v>10800</v>
       </c>
       <c r="D104" t="n">
-        <v/>
+        <v>11775</v>
       </c>
       <c r="E104" t="n">
         <v>11575</v>
@@ -7463,7 +7463,7 @@
         <v>120</v>
       </c>
       <c r="D105" t="n">
-        <v/>
+        <v>120</v>
       </c>
       <c r="E105" t="n">
         <v>121</v>
@@ -7513,7 +7513,7 @@
         <v>630</v>
       </c>
       <c r="D106" t="n">
-        <v/>
+        <v>640</v>
       </c>
       <c r="E106" t="n">
         <v>645</v>
@@ -7563,7 +7563,7 @@
         <v>306</v>
       </c>
       <c r="D107" t="n">
-        <v/>
+        <v>310</v>
       </c>
       <c r="E107" t="n">
         <v>318</v>
@@ -7613,7 +7613,7 @@
         <v>760</v>
       </c>
       <c r="D108" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E108" t="n">
         <v>705</v>
@@ -7663,7 +7663,7 @@
         <v>131</v>
       </c>
       <c r="D109" t="n">
-        <v/>
+        <v>132</v>
       </c>
       <c r="E109" t="n">
         <v>128</v>
@@ -7713,7 +7713,7 @@
         <v>216</v>
       </c>
       <c r="D110" t="n">
-        <v/>
+        <v>216</v>
       </c>
       <c r="E110" t="n">
         <v>210</v>
@@ -7763,7 +7763,7 @@
         <v>57</v>
       </c>
       <c r="D111" t="n">
-        <v/>
+        <v>58</v>
       </c>
       <c r="E111" t="n">
         <v>58</v>
@@ -7813,7 +7813,7 @@
         <v>103</v>
       </c>
       <c r="D112" t="n">
-        <v/>
+        <v>104</v>
       </c>
       <c r="E112" t="n">
         <v>111</v>
@@ -7863,7 +7863,7 @@
         <v>354</v>
       </c>
       <c r="D113" t="n">
-        <v/>
+        <v>356</v>
       </c>
       <c r="E113" t="n">
         <v>358</v>
@@ -7913,7 +7913,7 @@
         <v>1560</v>
       </c>
       <c r="D114" t="n">
-        <v/>
+        <v>1560</v>
       </c>
       <c r="E114" t="n">
         <v>1465</v>
@@ -7963,7 +7963,7 @@
         <v>165</v>
       </c>
       <c r="D115" t="n">
-        <v/>
+        <v>165</v>
       </c>
       <c r="E115" t="n">
         <v>157</v>
@@ -8013,7 +8013,7 @@
         <v>143</v>
       </c>
       <c r="D116" t="n">
-        <v/>
+        <v>144</v>
       </c>
       <c r="E116" t="n">
         <v>140</v>
@@ -8063,7 +8063,7 @@
         <v>114</v>
       </c>
       <c r="D117" t="n">
-        <v/>
+        <v>114</v>
       </c>
       <c r="E117" t="n">
         <v>115</v>
@@ -8113,7 +8113,7 @@
         <v>191</v>
       </c>
       <c r="D118" t="n">
-        <v/>
+        <v>191</v>
       </c>
       <c r="E118" t="n">
         <v>192</v>
@@ -8163,7 +8163,7 @@
         <v>8450</v>
       </c>
       <c r="D119" t="n">
-        <v/>
+        <v>8450</v>
       </c>
       <c r="E119" t="n">
         <v>8525</v>
@@ -8213,7 +8213,7 @@
         <v>68</v>
       </c>
       <c r="D120" t="n">
-        <v/>
+        <v>63</v>
       </c>
       <c r="E120" t="n">
         <v>68</v>
@@ -8263,7 +8263,7 @@
         <v>156</v>
       </c>
       <c r="D121" t="n">
-        <v/>
+        <v>157</v>
       </c>
       <c r="E121" t="n">
         <v>150</v>
@@ -8313,7 +8313,7 @@
         <v>111</v>
       </c>
       <c r="D122" t="n">
-        <v/>
+        <v>111</v>
       </c>
       <c r="E122" t="n">
         <v>112</v>
@@ -8363,7 +8363,7 @@
         <v>364</v>
       </c>
       <c r="D123" t="n">
-        <v/>
+        <v>366</v>
       </c>
       <c r="E123" t="n">
         <v>340</v>
@@ -8413,7 +8413,7 @@
         <v>153</v>
       </c>
       <c r="D124" t="n">
-        <v/>
+        <v>155</v>
       </c>
       <c r="E124" t="n">
         <v>159</v>
@@ -8463,7 +8463,7 @@
         <v>202</v>
       </c>
       <c r="D125" t="n">
-        <v/>
+        <v>202</v>
       </c>
       <c r="E125" t="n">
         <v>210</v>
@@ -8513,7 +8513,7 @@
         <v>342</v>
       </c>
       <c r="D126" t="n">
-        <v/>
+        <v>340</v>
       </c>
       <c r="E126" t="n">
         <v>340</v>
@@ -8563,7 +8563,7 @@
         <v>65</v>
       </c>
       <c r="D127" t="n">
-        <v/>
+        <v>66</v>
       </c>
       <c r="E127" t="n">
         <v>64</v>
@@ -8613,7 +8613,7 @@
         <v>59</v>
       </c>
       <c r="D128" t="n">
-        <v/>
+        <v>59</v>
       </c>
       <c r="E128" t="n">
         <v>58</v>
@@ -8663,7 +8663,7 @@
         <v>5475</v>
       </c>
       <c r="D129" t="n">
-        <v/>
+        <v>5475</v>
       </c>
       <c r="E129" t="n">
         <v>5250</v>
@@ -8713,7 +8713,7 @@
         <v>740</v>
       </c>
       <c r="D130" t="n">
-        <v/>
+        <v>745</v>
       </c>
       <c r="E130" t="n">
         <v>740</v>
@@ -8763,7 +8763,7 @@
         <v>1905</v>
       </c>
       <c r="D131" t="n">
-        <v/>
+        <v>1945</v>
       </c>
       <c r="E131" t="n">
         <v>1975</v>
@@ -8813,7 +8813,7 @@
         <v>121</v>
       </c>
       <c r="D132" t="n">
-        <v/>
+        <v>124</v>
       </c>
       <c r="E132" t="n">
         <v>125</v>
@@ -8863,7 +8863,7 @@
         <v>69</v>
       </c>
       <c r="D133" t="n">
-        <v/>
+        <v>70</v>
       </c>
       <c r="E133" t="n">
         <v>64</v>
@@ -8913,7 +8913,7 @@
         <v>800</v>
       </c>
       <c r="D134" t="n">
-        <v/>
+        <v>800</v>
       </c>
       <c r="E134" t="n">
         <v>750</v>
@@ -8963,7 +8963,7 @@
         <v>332</v>
       </c>
       <c r="D135" t="n">
-        <v/>
+        <v>332</v>
       </c>
       <c r="E135" t="n">
         <v>322</v>
@@ -9013,7 +9013,7 @@
         <v>93</v>
       </c>
       <c r="D136" t="n">
-        <v/>
+        <v>94</v>
       </c>
       <c r="E136" t="n">
         <v>93</v>
@@ -9063,7 +9063,7 @@
         <v>310</v>
       </c>
       <c r="D137" t="n">
-        <v/>
+        <v>310</v>
       </c>
       <c r="E137" t="n">
         <v>312</v>
@@ -9113,7 +9113,7 @@
         <v>133</v>
       </c>
       <c r="D138" t="n">
-        <v/>
+        <v>133</v>
       </c>
       <c r="E138" t="n">
         <v>114</v>
@@ -9163,7 +9163,7 @@
         <v>735</v>
       </c>
       <c r="D139" t="n">
-        <v/>
+        <v>735</v>
       </c>
       <c r="E139" t="n">
         <v>720</v>
@@ -9213,7 +9213,7 @@
         <v>234</v>
       </c>
       <c r="D140" t="n">
-        <v/>
+        <v>236</v>
       </c>
       <c r="E140" t="n">
         <v>234</v>
@@ -9263,7 +9263,7 @@
         <v>775</v>
       </c>
       <c r="D141" t="n">
-        <v/>
+        <v>780</v>
       </c>
       <c r="E141" t="n">
         <v>855</v>
@@ -9313,7 +9313,7 @@
         <v>4290</v>
       </c>
       <c r="D142" t="n">
-        <v/>
+        <v>4330</v>
       </c>
       <c r="E142" t="n">
         <v>4150</v>
@@ -9363,7 +9363,7 @@
         <v>238</v>
       </c>
       <c r="D143" t="n">
-        <v/>
+        <v>242</v>
       </c>
       <c r="E143" t="n">
         <v>234</v>
@@ -9413,7 +9413,7 @@
         <v>142</v>
       </c>
       <c r="D144" t="n">
-        <v/>
+        <v>141.85</v>
       </c>
       <c r="E144" t="n">
         <v>141</v>
@@ -9463,7 +9463,7 @@
         <v>144</v>
       </c>
       <c r="D145" t="n">
-        <v/>
+        <v>144</v>
       </c>
       <c r="E145" t="n">
         <v>143</v>
@@ -9513,7 +9513,7 @@
         <v>214</v>
       </c>
       <c r="D146" t="n">
-        <v/>
+        <v>216</v>
       </c>
       <c r="E146" t="n">
         <v>226</v>
@@ -9563,7 +9563,7 @@
         <v>76</v>
       </c>
       <c r="D147" t="n">
-        <v/>
+        <v>76</v>
       </c>
       <c r="E147" t="n">
         <v>74</v>
@@ -9613,7 +9613,7 @@
         <v>79</v>
       </c>
       <c r="D148" t="n">
-        <v/>
+        <v>79</v>
       </c>
       <c r="E148" t="n">
         <v>79</v>
@@ -9663,7 +9663,7 @@
         <v>725</v>
       </c>
       <c r="D149" t="n">
-        <v/>
+        <v>725</v>
       </c>
       <c r="E149" t="n">
         <v>715</v>
@@ -9713,7 +9713,7 @@
         <v>118</v>
       </c>
       <c r="D150" t="n">
-        <v/>
+        <v>118</v>
       </c>
       <c r="E150" t="n">
         <v>128</v>
@@ -9763,7 +9763,7 @@
         <v>3650</v>
       </c>
       <c r="D151" t="n">
-        <v/>
+        <v>3650</v>
       </c>
       <c r="E151" t="n">
         <v>3690</v>
@@ -9813,7 +9813,7 @@
         <v>765</v>
       </c>
       <c r="D152" t="n">
-        <v/>
+        <v>765</v>
       </c>
       <c r="E152" t="n">
         <v>775</v>
@@ -9863,7 +9863,7 @@
         <v>3730</v>
       </c>
       <c r="D153" t="n">
-        <v/>
+        <v>3730</v>
       </c>
       <c r="E153" t="n">
         <v>4000</v>
@@ -9913,7 +9913,7 @@
         <v>645</v>
       </c>
       <c r="D154" t="n">
-        <v/>
+        <v>650</v>
       </c>
       <c r="E154" t="n">
         <v>635</v>
@@ -9963,7 +9963,7 @@
         <v>157</v>
       </c>
       <c r="D155" t="n">
-        <v/>
+        <v>159</v>
       </c>
       <c r="E155" t="n">
         <v>155</v>
@@ -10013,7 +10013,7 @@
         <v>885</v>
       </c>
       <c r="D156" t="n">
-        <v/>
+        <v>890</v>
       </c>
       <c r="E156" t="n">
         <v>865</v>
@@ -10063,7 +10063,7 @@
         <v>156</v>
       </c>
       <c r="D157" t="n">
-        <v/>
+        <v>156</v>
       </c>
       <c r="E157" t="n">
         <v>157</v>
@@ -10113,7 +10113,7 @@
         <v>540</v>
       </c>
       <c r="D158" t="n">
-        <v/>
+        <v>540</v>
       </c>
       <c r="E158" t="n">
         <v>535</v>
@@ -10163,7 +10163,7 @@
         <v>150</v>
       </c>
       <c r="D159" t="n">
-        <v/>
+        <v>150</v>
       </c>
       <c r="E159" t="n">
         <v>171</v>
@@ -10213,7 +10213,7 @@
         <v>157</v>
       </c>
       <c r="D160" t="n">
-        <v/>
+        <v>158</v>
       </c>
       <c r="E160" t="n">
         <v>157</v>
@@ -10263,7 +10263,7 @@
         <v>2060</v>
       </c>
       <c r="D161" t="n">
-        <v/>
+        <v>2080</v>
       </c>
       <c r="E161" t="n">
         <v>2050</v>
@@ -10313,7 +10313,7 @@
         <v>580</v>
       </c>
       <c r="D162" t="n">
-        <v/>
+        <v>585</v>
       </c>
       <c r="E162" t="n">
         <v>570</v>
@@ -10363,7 +10363,7 @@
         <v>145</v>
       </c>
       <c r="D163" t="n">
-        <v/>
+        <v>140</v>
       </c>
       <c r="E163" t="n">
         <v>137</v>
@@ -10413,7 +10413,7 @@
         <v>154</v>
       </c>
       <c r="D164" t="n">
-        <v/>
+        <v>155</v>
       </c>
       <c r="E164" t="n">
         <v>153</v>
@@ -10463,7 +10463,7 @@
         <v>103</v>
       </c>
       <c r="D165" t="n">
-        <v/>
+        <v>104</v>
       </c>
       <c r="E165" t="n">
         <v>119</v>
